--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.58075788935679</v>
+        <v>8.706873157020478</v>
       </c>
       <c r="D2" t="n">
-        <v>53.41007246915212</v>
+        <v>8.67913677623722</v>
       </c>
       <c r="E2" t="n">
-        <v>8.483885345415727</v>
+        <v>1.378631368630056</v>
       </c>
       <c r="F2" t="n">
-        <v>15.16007550646532</v>
+        <v>2.463512269800615</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.22164502650546</v>
+        <v>7.511017316807137</v>
       </c>
       <c r="D3" t="n">
-        <v>46.03003649699173</v>
+        <v>7.479880930761156</v>
       </c>
       <c r="E3" t="n">
-        <v>8.483885345415727</v>
+        <v>1.378631368630056</v>
       </c>
       <c r="F3" t="n">
-        <v>15.16007550646532</v>
+        <v>2.463512269800615</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.01973007817718</v>
+        <v>8.290706137703792</v>
       </c>
       <c r="D4" t="n">
-        <v>50.91259130820237</v>
+        <v>8.273296087582885</v>
       </c>
       <c r="E4" t="n">
-        <v>8.483885345415727</v>
+        <v>1.378631368630056</v>
       </c>
       <c r="F4" t="n">
-        <v>15.16007550646532</v>
+        <v>2.463512269800615</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.84289920552397</v>
+        <v>5.824471120897646</v>
       </c>
       <c r="D5" t="n">
-        <v>35.87511577710124</v>
+        <v>5.829706313778952</v>
       </c>
       <c r="E5" t="n">
-        <v>8.483885345415727</v>
+        <v>1.378631368630056</v>
       </c>
       <c r="F5" t="n">
-        <v>15.16007550646532</v>
+        <v>2.463512269800615</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.78718049035502</v>
+        <v>5.652916829682691</v>
       </c>
       <c r="D6" t="n">
-        <v>16.62187700614228</v>
+        <v>2.701055013498121</v>
       </c>
       <c r="E6" t="n">
-        <v>8.483885345415727</v>
+        <v>1.378631368630056</v>
       </c>
       <c r="F6" t="n">
-        <v>15.16007550646532</v>
+        <v>2.463512269800615</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.20080853405828</v>
+        <v>4.907631386784471</v>
       </c>
       <c r="D7" t="n">
-        <v>30.34192922800548</v>
+        <v>4.930563499550891</v>
       </c>
       <c r="E7" t="n">
-        <v>8.483885345415727</v>
+        <v>1.378631368630056</v>
       </c>
       <c r="F7" t="n">
-        <v>15.16007550646532</v>
+        <v>2.463512269800615</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.99177142468859</v>
+        <v>5.686162856511896</v>
       </c>
       <c r="D8" t="n">
-        <v>11.87481967905903</v>
+        <v>1.929658197847093</v>
       </c>
       <c r="E8" t="n">
-        <v>8.483885345415727</v>
+        <v>1.378631368630056</v>
       </c>
       <c r="F8" t="n">
-        <v>15.16007550646532</v>
+        <v>2.463512269800615</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
